--- a/Game/Race.xlsx
+++ b/Game/Race.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Steam\steamapps\common\Elin\Package\_Lang_Vietnamese\Lang\VN\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425F2081-7266-4F6D-AE68-EB854F36050B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D743E49C-AF12-41CA-841D-CF0F8BE76D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Race" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Race!$A$2:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Race!$A$2:$H$95</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="279">
   <si>
     <t>id</t>
   </si>
@@ -52,13 +52,16 @@
     <t>yerles</t>
   </si>
   <si>
+    <t>EA 23.295</t>
+  </si>
+  <si>
     <t>イエルス</t>
   </si>
   <si>
     <t>The Yerles, people of the rising New Kingdom in Sierre Terre, trace their lineage back to slaves who escaped from Eulderna. Harboring deep-seated hatred towards the empire and everything it represents; they have established the pinnacle of mechanical civilizations in Sierre. Gifted with a heightened learning capacity, adept in handling mechanized armaments, they acquire feats faster than any other races.</t>
   </si>
   <si>
-    <t>シエラ・テールで急速に台頭してきた新王国イエルの民がイェルスです。彼らの祖先はエウダーナから脱走した奴隷であり、帝国と帝国の生み出した全てのものを憎んでいます。シエラ随一の機械文明を築き上げた彼らは、高い学習能力を持ち、機械武装の扱いにたけ、他の種族よりも早くフィートを獲得できます。</t>
+    <t>シエラ・テールで急速に台頭してきた新王国イエルの民がイエルスです。彼らの祖先はエウダーナから脱走した奴隷であり、帝国と帝国の生み出した全てのものを憎んでいます。シエラ随一の機械文明を築き上げた彼らは、高い学習能力を持ち、機械武装の扱いにたけ、他の種族よりも早くフィートを獲得できます。</t>
   </si>
   <si>
     <t>eulderna</t>
@@ -286,6 +289,18 @@
     <t>古代蟹は最も古い蟹の種族で、水辺を好み、生息する地域に適応し様々な属性へと進化しています。基本的には美味しいものの、属性によって風味も変化します。筋力と耐久に秀で、その巨大なハサミで敵を拘束し、また泡のブレスを吐くことができます。</t>
   </si>
   <si>
+    <t>ratkin</t>
+  </si>
+  <si>
+    <t>ラトキン</t>
+  </si>
+  <si>
+    <t>werewolf</t>
+  </si>
+  <si>
+    <t>人狼</t>
+  </si>
+  <si>
     <t>goblin</t>
   </si>
   <si>
@@ -343,6 +358,12 @@
     <t>スライム</t>
   </si>
   <si>
+    <t>Slimes are amorphous, gelatinous beings with bodies that lack a fixed shape. They may appear fragile and are often called the weakest of monsters, yet they possess a mysterious potential to absorb whatever they take in and transform it into their own strength. Even if you were to awaken one day as a slime, there would be no need to despair. That humble body is merely the beginning of an endless path of evolution.</t>
+  </si>
+  <si>
+    <t>スライムは不定形の体を持つ粘体生物です。見た目は頼りなく、最弱の魔物と呼ばれることもありますが、あらゆるものを取り込み、自らの力へと変えていく不思議な可能性を秘めています。もし目覚めたときに自分がスライムだったとしても、嘆く必要はありません。その体は、無限の進化へと続く始まりなのです。</t>
+  </si>
+  <si>
     <t>wolf</t>
   </si>
   <si>
@@ -361,6 +382,15 @@
     <t>ウサギ</t>
   </si>
   <si>
+    <t>rabbitkin</t>
+  </si>
+  <si>
+    <t>ravian</t>
+  </si>
+  <si>
+    <t>ラビアン</t>
+  </si>
+  <si>
     <t>sheep</t>
   </si>
   <si>
@@ -721,7 +751,7 @@
     <t>神</t>
   </si>
   <si>
-    <t>EA 23.19</t>
+    <t>EA 23.281</t>
   </si>
   <si>
     <t>Alpha 15.1</t>
@@ -769,7 +799,7 @@
     <t>nhân mã</t>
   </si>
   <si>
-    <t>Yerles là cư dân của Vương quốc mới đang trỗi dậy tại Sierre Terre. Tổ tiên họ là những nô lệ thoát khỏi tay Eulderna, mang trong lòng căm ghét đế quốc cùng mọi thứ mà nó tạo ra. Họ đã xây dựng nền văn minh cơ khí tiên tiến nhất tại Sierre, sở hữu khả năng học hỏi vượt trội, thành thạo vũ khí cơ khí, và có thể nhanh chóng đạt được thành tựu hơn bất kỳ chủng tộc nào khác.</t>
+    <t>Yerles là dân cư của Tân Vương quốc đang trỗi dậy mạnh mẽ tại Sierre Terre. Tổ tiên của họ vốn là những nô lệ đào thoát khỏi Eulderna, mang trong mình lòng căm thù sâu sắc đối với đế chế và tất cả những gì nó đại diện. Họ đã xây dựng nên đỉnh cao của văn minh cơ khí tại Sierre. Nhờ khả năng học hỏi vượt trội và sự tinh thông trong việc sử dụng vũ khí cơ giới, họ có thể nhận được các thiên phú nhanh hơn bất kỳ chủng tộc nào khác.</t>
   </si>
   <si>
     <t>Eulderna là một trong những quốc gia cổ xưa nhất tại Sierre Terre. Họ sở hữu kiến thức sâu rộng về ma pháp và vũ khí ma thuật, được thế giới biết đến và e sợ dưới danh xưng Đế quốc sa mạc. Họ là những kẻ theo đuổi chủ nghĩa tàn nhẫn với ý thức chọn lọc, tin rằng chỉ mình họ xứng đáng quyết định cục diện thế giới. Người Eulderna thành thạo sử dụng ma pháp và đồ vật ma thuật, phù hợp với các vai trò pháp sư hoặc chiến binh trung gian.</t>
@@ -811,6 +841,9 @@
     <t>Succubi, còn được gọi là “Hồn Trăng” hay “Lunar”, theo truyền thuyết sẽ xuất hiện bên gối của con người vào những đêm trăng sáng để quyến rũ. Thực tế, bất kể trăng sáng hay không, ngày hay đêm, chúng đều yêu thích những thú vui khoái lạc. Chúng sở hữu sức quyến rũ và ma lực cao, và càng trở nên mạnh mẽ khi đắm chìm trong khoái cảm.</t>
   </si>
   <si>
+    <t>Ma cà rồng từ cổ chí kim đã luôn là chủng tộc đáng sợ, được mệnh danh là những kẻ thống trị đêm đen với thể chất phi thường và trí tuệ sắc sảo. Chúng sở hữu năng lực vượt trội khi ẩn mình trong bóng tối, nhưng lại yếu ớt trước ánh sáng mặt trời và lửa. Do không thể duy trì sự sống bằng thức ăn thông thường, chúng luôn khao khát những dòng máu tươi còn nóng hổi.</t>
+  </si>
+  <si>
     <t>Bán thần là những đứa trẻ sinh ra từ sự kết hợp giữa hiện thân của thần giáng xuống trần gian và con người. Phần lớn trong số họ chỉ là kết quả của trò đùa thoáng qua của các vị thần, và hiếm khi nhận thức được nguồn gốc hay năng lực đặc biệt của bản thân. Họ sở hữu nhan sắc như thần, khả năng cân bằng, sinh lực dồi dào và ma lực mạnh mẽ.</t>
   </si>
   <si>
@@ -823,7 +856,10 @@
     <t>Cua Cổ Đại là chủng loài cua lâu đời nhất, ưa sống gần nguồn nước và tiến hóa theo các thuộc tính khác nhau tùy theo môi trường sinh sống. Chúng nhìn chung rất ngon, nhưng hương vị cũng thay đổi theo từng thuộc tính. Cua Cổ Đại sở hữu sức mạnh và thể chất vượt trội, có thể kìm giữ kẻ thù bằng chiếc càng khổng lồ, đồng thời có khả năng phun hơi bọt.</t>
   </si>
   <si>
-    <t>Ma cà rồng từ cổ chí kim đã luôn là chủng tộc đáng sợ, được mệnh danh là những kẻ thống trị đêm đen với thể chất phi thường và trí tuệ sắc sảo. Chúng sở hữu năng lực vượt trội khi ẩn mình trong bóng tối, nhưng lại yếu ớt trước ánh sáng mặt trời và lửa. Do không thể duy trì sự sống bằng thức ăn thông thường, chúng luôn khao khát những dòng máu tươi còn nóng hổi.</t>
+    <t>Slime là những sinh vật thể nhầy có thân hình bất định. Tuy vẻ ngoài mỏng manh và thường bị coi là loài quái vật yếu nhất, nhưng chúng lại ẩn chứa một tiềm năng huyền bí: hấp thụ mọi thứ và biến thành sức mạnh của chính mình. Dẫu một ngày thức dậy và nhận ra mình đã biến thành một con Slime, bạn cũng không cần phải tuyệt vọng. Bởi cơ thể khiêm nhường ấy chính là điểm khởi đầu cho một hành trình tiến hóa vô tận.</t>
+  </si>
+  <si>
+    <t>người sói</t>
   </si>
 </sst>
 </file>
@@ -1181,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="8" width="16" customWidth="1" collapsed="1"/>
@@ -1218,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -1227,512 +1263,512 @@
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C19" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>234</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>278</v>
       </c>
       <c r="D23" t="s">
         <v>90</v>
@@ -1746,7 +1782,7 @@
         <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C24" t="s">
         <v>92</v>
@@ -1763,1159 +1799,1219 @@
         <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="F32" t="s">
+        <v>277</v>
+      </c>
+      <c r="G32" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D35" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B36" t="s">
-        <v>234</v>
+        <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E36" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B37" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B38" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C38" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C39" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E39" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B40" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D40" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E40" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B41" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E41" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D43" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E43" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B44" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D44" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E44" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B45" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E45" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B46" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E46" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B47" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B48" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D48" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E48" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B49" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C49" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B50" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C50" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E50" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B51" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C51" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E51" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B52" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C52" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D52" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B53" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C53" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D53" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E53" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B54" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C54" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D54" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E54" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C55" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D55" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E55" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B56" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C56" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D56" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E56" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B57" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C57" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D57" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E57" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B58" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C58" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D58" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E58" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B59" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C59" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D59" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E59" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B60" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C60" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D60" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E60" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B61" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C61" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D61" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E61" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B62" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C62" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D62" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E62" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B63" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C63" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E63" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B64" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C64" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D64" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E64" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B65" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C65" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D65" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E65" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B66" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C66" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D66" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E66" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B67" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C67" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D67" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E67" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B68" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C68" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D68" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E68" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B69" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C69" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D69" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E69" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B70" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C70" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D70" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E70" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B71" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C71" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D71" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E71" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B72" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C72" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D72" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E72" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B73" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C73" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D73" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E73" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B74" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C74" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D74" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E74" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B75" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D75" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E75" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B76" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D76" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E76" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B77" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C77" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D77" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E77" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B78" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C78" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D78" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E78" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B79" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C79" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D79" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E79" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B80" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C80" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D80" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E80" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B81" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C81" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D81" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E81" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B82" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="C82" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D82" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E82" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B83" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C83" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D83" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E83" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B84" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C84" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D84" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E84" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B85" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C85" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D85" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E85" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B86" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C86" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D86" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E86" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B87" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C87" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D87" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E87" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B88" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="C88" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D88" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E88" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B89" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C89" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D89" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E89" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B90" t="s">
         <v>244</v>
       </c>
       <c r="C90" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D90" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E90" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B91" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C91" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D91" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E91" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B92" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C92" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D92" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E92" t="s">
-        <v>231</v>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>235</v>
+      </c>
+      <c r="B93" t="s">
+        <v>254</v>
+      </c>
+      <c r="C93" t="s">
+        <v>235</v>
+      </c>
+      <c r="D93" t="s">
+        <v>235</v>
+      </c>
+      <c r="E93" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>237</v>
+      </c>
+      <c r="B94" t="s">
+        <v>248</v>
+      </c>
+      <c r="C94" t="s">
+        <v>238</v>
+      </c>
+      <c r="D94" t="s">
+        <v>238</v>
+      </c>
+      <c r="E94" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>240</v>
+      </c>
+      <c r="B95" t="s">
+        <v>255</v>
+      </c>
+      <c r="C95" t="s">
+        <v>240</v>
+      </c>
+      <c r="D95" t="s">
+        <v>240</v>
+      </c>
+      <c r="E95" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:H95" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>